--- a/assets/samples/sample_rcm.xlsx
+++ b/assets/samples/sample_rcm.xlsx
@@ -12,14 +12,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="77">
   <si>
     <t>業務</t>
   </si>
   <si>
+    <t>工程No.</t>
+  </si>
+  <si>
+    <t>リスクID</t>
+  </si>
+  <si>
     <t>リスクの内容</t>
   </si>
   <si>
+    <t>統制ID</t>
+  </si>
+  <si>
     <t>統制の内容</t>
   </si>
   <si>
@@ -32,9 +41,6 @@
     <t>評価内容</t>
   </si>
   <si>
-    <t>統制ID</t>
-  </si>
-  <si>
     <t>予防・発見</t>
   </si>
   <si>
@@ -86,9 +92,18 @@
     <t>承認</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R001</t>
+  </si>
+  <si>
     <t>与信限度超過取引による回収不能</t>
   </si>
   <si>
+    <t>C001</t>
+  </si>
+  <si>
     <t>受注時にシステムが与信限度残高を自動チェックし、超過時は受注を保留する</t>
   </si>
   <si>
@@ -104,9 +119,6 @@
     <t>－</t>
   </si>
   <si>
-    <t>C001 キー統制</t>
-  </si>
-  <si>
     <t>予防</t>
   </si>
   <si>
@@ -137,9 +149,18 @@
     <t>出荷</t>
   </si>
   <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>R002</t>
+  </si>
+  <si>
     <t>出荷指図と異なる数量・品目の出荷による誤った売上</t>
   </si>
   <si>
+    <t>C002</t>
+  </si>
+  <si>
     <t>出荷担当が出荷指図書と現品(数量・品目)を照合し一致を確認のうえ出荷</t>
   </si>
   <si>
@@ -149,9 +170,6 @@
     <t>（旧データ：一部不備）</t>
   </si>
   <si>
-    <t>C002 キー統制</t>
-  </si>
-  <si>
     <t>手動</t>
   </si>
   <si>
@@ -167,13 +185,19 @@
     <t>売上計上</t>
   </si>
   <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>R003</t>
+  </si>
+  <si>
     <t>出荷を伴わない架空売上又は期ズレ計上</t>
   </si>
   <si>
+    <t>C003</t>
+  </si>
+  <si>
     <t>注文・出荷・請求の三者照合で一致した取引のみ売上計上</t>
-  </si>
-  <si>
-    <t>C003 キー統制</t>
   </si>
   <si>
     <t>発見</t>
@@ -336,13 +360,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -712,30 +739,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:X5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="11" customWidth="1"/>
-    <col min="13" max="14" width="7" customWidth="1"/>
-    <col min="15" max="16" width="6" customWidth="1"/>
-    <col min="17" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="13" customWidth="1"/>
-    <col min="19" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="12" width="6" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="24" customWidth="1"/>
+    <col min="15" max="18" width="6" customWidth="1"/>
+    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="20" max="20" width="24" customWidth="1"/>
+    <col min="21" max="22" width="6" customWidth="1"/>
+    <col min="23" max="23" width="26" customWidth="1"/>
+    <col min="24" max="24" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" ht="69" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -745,36 +768,36 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
       <c r="M1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="R1" s="1" t="s">
@@ -786,262 +809,288 @@
       <c r="T1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="W1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" ht="95" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="K2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="3"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="3" t="s">
+    <row r="3" ht="31" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="B3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="D3" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>31</v>
       </c>
+      <c r="H3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="N3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" ht="31" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="H4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="U4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="X4" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="N5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="T3" s="4" t="s">
+      <c r="O5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="R5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="U3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="S5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="U5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="V5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="6" t="s">
+      <c r="W5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X5" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="T4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="U4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="V4" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="D1:I1"/>
+  <mergeCells count="19">
+    <mergeCell ref="G1:L1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
@@ -1052,6 +1101,8 @@
     <mergeCell ref="T1:T2"/>
     <mergeCell ref="U1:U2"/>
     <mergeCell ref="V1:V2"/>
+    <mergeCell ref="W1:W2"/>
+    <mergeCell ref="X1:X2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1072,89 +1123,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>64</v>
+      <c r="A1" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" s="9">
+      <c r="A2" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="10">
         <v>3</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="10">
         <v>3</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="10">
         <v>0</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="10">
         <v>3</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="10">
         <v>0</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="10">
         <v>0</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="11">
+      <c r="A3" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="12">
         <v>3</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="12">
         <v>3</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="12">
         <v>0</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="12">
         <v>3</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="12">
         <v>0</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="12">
         <v>0</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>68</v>
+      <c r="A5" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/assets/samples/sample_rcm.xlsx
+++ b/assets/samples/sample_rcm.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="x" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="評価結果サマリ" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="65">
   <si>
     <t>業務</t>
   </si>
@@ -207,49 +206,13 @@
   </si>
   <si>
     <t>三者照合チェックリスト</t>
-  </si>
-  <si>
-    <t>プロセス</t>
-  </si>
-  <si>
-    <t>統制数</t>
-  </si>
-  <si>
-    <t>キー統制</t>
-  </si>
-  <si>
-    <t>整備評価済</t>
-  </si>
-  <si>
-    <t>運用評価済</t>
-  </si>
-  <si>
-    <t>不備件数</t>
-  </si>
-  <si>
-    <t>うち開示すべき重要な不備</t>
-  </si>
-  <si>
-    <t>例外件数</t>
-  </si>
-  <si>
-    <t>販売プロセス（受注〜売上計上）</t>
-  </si>
-  <si>
-    <t>【合計】</t>
-  </si>
-  <si>
-    <t>全社結論</t>
-  </si>
-  <si>
-    <t>財務報告に係る内部統制は有効である（候補）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -268,29 +231,8 @@
       <sz val="10"/>
       <name val="Yu Gothic"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Yu Gothic"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Yu Gothic"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Yu Gothic"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF157F5B"/>
-      <sz val="10"/>
-      <name val="Yu Gothic"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -305,16 +247,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFf1f8f6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0E7C73"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF4F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -360,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -383,23 +315,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1107,109 +1022,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="3" width="10" customWidth="1"/>
-    <col min="4" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="10">
-        <v>3</v>
-      </c>
-      <c r="C2" s="10">
-        <v>3</v>
-      </c>
-      <c r="D2" s="10">
-        <v>0</v>
-      </c>
-      <c r="E2" s="10">
-        <v>3</v>
-      </c>
-      <c r="F2" s="10">
-        <v>0</v>
-      </c>
-      <c r="G2" s="10">
-        <v>0</v>
-      </c>
-      <c r="H2" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" s="12">
-        <v>3</v>
-      </c>
-      <c r="C3" s="12">
-        <v>3</v>
-      </c>
-      <c r="D3" s="12">
-        <v>0</v>
-      </c>
-      <c r="E3" s="12">
-        <v>3</v>
-      </c>
-      <c r="F3" s="12">
-        <v>0</v>
-      </c>
-      <c r="G3" s="12">
-        <v>0</v>
-      </c>
-      <c r="H3" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>
--- a/assets/samples/sample_rcm.xlsx
+++ b/assets/samples/sample_rcm.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="64">
   <si>
     <t>業務</t>
   </si>
@@ -109,7 +109,7 @@
     <t>·</t>
   </si>
   <si>
-    <t>✓</t>
+    <t>○</t>
   </si>
   <si>
     <t>△ 一部不備</t>
@@ -122,9 +122,6 @@
   </si>
   <si>
     <t>自動</t>
-  </si>
-  <si>
-    <t>○</t>
   </si>
   <si>
     <t>都度</t>
@@ -825,48 +822,48 @@
         <v>36</v>
       </c>
       <c r="Q3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="S3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="T3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="U3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="V3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="V3" s="5" t="s">
+      <c r="W3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="4" ht="31" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>32</v>
@@ -887,60 +884,60 @@
         <v>31</v>
       </c>
       <c r="M4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="O4" s="7" t="s">
         <v>35</v>
       </c>
       <c r="P4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S4" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="T4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="U4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="V4" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="R4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="T4" s="6" t="s">
+      <c r="W4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="X4" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="U4" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="V4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="W4" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="X4" s="7" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" ht="31" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>32</v>
@@ -967,34 +964,34 @@
         <v>34</v>
       </c>
       <c r="O5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="S5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="P5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q5" s="5" t="s">
+      <c r="T5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="V5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="R5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="V5" s="5" t="s">
+      <c r="W5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X5" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="X5" s="5" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
